--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -604,21 +604,21 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | suspicious token(s): 4c (letter/digit mix) :: And for further relief ; pray subpÃ¦na, 4c.</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: under the will dated theâ€”-</t>
-        </is>
-      </c>
+          <t>L139: suspicious token(s): 4c (letter/digit mix) :: And for further relief ; pray subpæna, 4c.</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”If 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]126 ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]126 ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L14: isolated marker/symbol line :: 3.</t>
@@ -661,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -674,16 +674,8 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NorE.â€”This form may be varied accord</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”This form may be varied according to the circumstances</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -737,16 +729,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: rther relief: pray subpanaÃ¦na, &amp;c.</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: intestates, of ---------,late of -------â€”, who died on</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -754,7 +738,11 @@
           <t>L42: isolated marker/symbol line :: 6</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L149: isolated marker/symbol line :: — ,</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
@@ -782,12 +770,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -796,16 +784,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: payment of his share thÃ©thereof.</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: estate of the said ------1â€”, deceased, and that C. D.,</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -855,16 +835,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: ther relief; pray subpa Ã¦ na, &amp; c.</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”â€”, but ne</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -876,7 +848,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: intestates, of ---------,late of -------â€”, who died on</t>
+          <t>L77: punctuation artifact: double/multiple hyphen :: intestates, of ---------,late of -------—, who died on</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -915,11 +887,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: about theâ€”</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
@@ -966,11 +934,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the (or the said A. B.â€™s share of the) personal estate of</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
@@ -978,7 +942,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: estate of the said ------1â€”, deceased, and that C. D.,</t>
+          <t>L82: punctuation artifact: double/multiple hyphen :: estate of the said ------1—, deceased, and that C. D.,</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1013,11 +977,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | suspicious token(s): 4c (letter/digit mix) :: And for further relief ; pray subpÃ¦na, 4c.</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
@@ -1045,12 +1005,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1060,11 +1020,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” ,</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1093,7 +1049,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1132,7 +1088,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
